--- a/Treinamento hackaton/despesas-Tratado.xlsx
+++ b/Treinamento hackaton/despesas-Tratado.xlsx
@@ -5,16 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\53282601808\Desktop\Treinamento hackaton\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\53282601808\Desktop\Atividades-Senai\Treinamento hackaton\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB0C4822-8777-4DB8-BC32-A6AEC2FCCAB6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A76517-5914-4E24-92B3-0B3B6C1ABC22}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8364" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8364" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$175</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -957,10 +960,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1268,7 +1274,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.109375" style="2" customWidth="1"/>
     <col min="3" max="3" width="19.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
@@ -1297,150 +1303,150 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
+        <v>193</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>280</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E2">
-        <v>11670.1</v>
+        <v>8588.7999999999993</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>281</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
+        <v>20</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="E3">
-        <v>17394.82</v>
+        <v>6849.85</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
+        <v>57</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>105</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E4">
-        <v>19787.46</v>
+        <v>2580.04</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
+        <v>187</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>272</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E5">
-        <v>2159.77</v>
+        <v>1026.0999999999999</v>
       </c>
       <c r="F5" t="s">
-        <v>19</v>
+        <v>273</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
+        <v>121</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>195</v>
       </c>
       <c r="C6" t="s">
         <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E6">
-        <v>7390.2</v>
+        <v>16317.04</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
+        <v>196</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>24</v>
+        <v>78</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>134</v>
       </c>
       <c r="C7" t="s">
         <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E7">
-        <v>5786.35</v>
+        <v>12378.33</v>
       </c>
       <c r="F7" t="s">
-        <v>25</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
+        <v>148</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" t="s">
-        <v>17</v>
-      </c>
       <c r="D8" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E8">
-        <v>12713.59</v>
+        <v>101064.7</v>
       </c>
       <c r="F8" t="s">
-        <v>27</v>
+        <v>225</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
+        <v>151</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>228</v>
       </c>
       <c r="C9" t="s">
         <v>29</v>
@@ -1449,198 +1455,198 @@
         <v>30</v>
       </c>
       <c r="E9">
-        <v>11286.99</v>
+        <v>11345.68</v>
       </c>
       <c r="F9" t="s">
-        <v>31</v>
+        <v>229</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>32</v>
+        <v>157</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>236</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E10">
-        <v>398.2</v>
+        <v>5352.15</v>
       </c>
       <c r="F10" t="s">
-        <v>33</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>34</v>
+        <v>160</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>240</v>
       </c>
       <c r="C11" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D11" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E11">
-        <v>10511.56</v>
+        <v>1884.31</v>
       </c>
       <c r="F11" t="s">
-        <v>35</v>
+        <v>241</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>36</v>
+        <v>163</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>238</v>
       </c>
       <c r="C12" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="D12" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="E12">
-        <v>14855</v>
+        <v>12551.21</v>
       </c>
       <c r="F12" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>37</v>
+        <v>8</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="C13" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="D13" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E13">
-        <v>14020.35</v>
+        <v>11286.99</v>
       </c>
       <c r="F13" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>39</v>
+        <v>172</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>252</v>
       </c>
       <c r="C14" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D14" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E14">
-        <v>15504.96</v>
+        <v>14432.77</v>
       </c>
       <c r="F14" t="s">
-        <v>40</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>41</v>
+        <v>63</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>117</v>
       </c>
       <c r="C15" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="D15" t="s">
         <v>30</v>
       </c>
       <c r="E15">
-        <v>10878.01</v>
+        <v>14912.48</v>
       </c>
       <c r="F15" t="s">
-        <v>42</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>34</v>
+        <v>95</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>156</v>
       </c>
       <c r="C16" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="D16" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E16">
-        <v>6450.78</v>
+        <v>15524</v>
       </c>
       <c r="F16" t="s">
-        <v>43</v>
+        <v>157</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>18</v>
-      </c>
-      <c r="B17" t="s">
-        <v>44</v>
+        <v>54</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>57</v>
       </c>
       <c r="C17" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D17" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E17">
-        <v>15605.07</v>
+        <v>1396.9</v>
       </c>
       <c r="F17" t="s">
-        <v>45</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>19</v>
-      </c>
-      <c r="B18" t="s">
-        <v>46</v>
+        <v>152</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>230</v>
       </c>
       <c r="C18" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="D18" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E18">
-        <v>11327.78</v>
+        <v>12213.03</v>
       </c>
       <c r="F18" t="s">
-        <v>47</v>
+        <v>149</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>20</v>
-      </c>
-      <c r="B19" t="s">
-        <v>48</v>
+        <v>129</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>204</v>
       </c>
       <c r="C19" t="s">
         <v>21</v>
@@ -1649,197 +1655,197 @@
         <v>30</v>
       </c>
       <c r="E19">
-        <v>6849.85</v>
+        <v>2048.67</v>
       </c>
       <c r="F19" t="s">
-        <v>49</v>
+        <v>205</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>21</v>
-      </c>
-      <c r="B20" t="s">
-        <v>50</v>
+        <v>68</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="C20" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D20" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E20">
-        <v>814.96</v>
+        <v>45438.400000000001</v>
       </c>
       <c r="F20" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>22</v>
-      </c>
-      <c r="B21" t="s">
-        <v>52</v>
+        <v>191</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>279</v>
       </c>
       <c r="C21" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D21" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E21">
-        <v>7317.09</v>
+        <v>4004.41</v>
       </c>
       <c r="F21" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>23</v>
-      </c>
-      <c r="B22" t="s">
-        <v>54</v>
+        <v>40</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="C22" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D22" t="s">
         <v>30</v>
       </c>
       <c r="E22">
-        <v>12181.89</v>
+        <v>16353.44</v>
       </c>
       <c r="F22" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>24</v>
-      </c>
-      <c r="B23" t="s">
-        <v>56</v>
+        <v>77</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>132</v>
       </c>
       <c r="C23" t="s">
         <v>7</v>
       </c>
       <c r="D23" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E23">
-        <v>8180.55</v>
+        <v>14771.55</v>
       </c>
       <c r="F23" t="s">
-        <v>33</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>25</v>
-      </c>
-      <c r="B24" t="s">
-        <v>57</v>
+        <v>190</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>132</v>
       </c>
       <c r="C24" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D24" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E24">
-        <v>13129.43</v>
+        <v>13550.61</v>
       </c>
       <c r="F24" t="s">
-        <v>58</v>
+        <v>278</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>26</v>
-      </c>
-      <c r="B25" t="s">
-        <v>59</v>
+        <v>147</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>223</v>
       </c>
       <c r="C25" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D25" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E25">
-        <v>10062.76</v>
+        <v>18391.28</v>
       </c>
       <c r="F25" t="s">
-        <v>60</v>
+        <v>149</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>28</v>
-      </c>
-      <c r="B26" t="s">
-        <v>61</v>
+        <v>60</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>111</v>
       </c>
       <c r="C26" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="D26" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="E26">
-        <v>16226.08</v>
+        <v>190090</v>
       </c>
       <c r="F26" t="s">
-        <v>38</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27">
+        <v>67</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C27" t="s">
         <v>29</v>
       </c>
-      <c r="B27" t="s">
-        <v>62</v>
-      </c>
-      <c r="C27" t="s">
-        <v>21</v>
-      </c>
       <c r="D27" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E27">
-        <v>18045.12</v>
+        <v>11939.42</v>
       </c>
       <c r="F27" t="s">
-        <v>63</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>30</v>
-      </c>
-      <c r="B28" t="s">
-        <v>64</v>
+        <v>146</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>222</v>
       </c>
       <c r="C28" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D28" t="s">
         <v>30</v>
       </c>
       <c r="E28">
-        <v>2865.12</v>
+        <v>12982.56</v>
       </c>
       <c r="F28" t="s">
-        <v>65</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>31</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C29" t="s">
@@ -1857,290 +1863,290 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>32</v>
-      </c>
-      <c r="B30" t="s">
-        <v>68</v>
+        <v>44</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="C30" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D30" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E30">
-        <v>570.52</v>
+        <v>14763.4</v>
       </c>
       <c r="F30" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>33</v>
-      </c>
-      <c r="B31" t="s">
-        <v>70</v>
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="C31" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D31" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="E31">
-        <v>17704.330000000002</v>
+        <v>2865.12</v>
       </c>
       <c r="F31" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>34</v>
-      </c>
-      <c r="B32" t="s">
-        <v>72</v>
+        <v>115</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>187</v>
       </c>
       <c r="C32" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="E32">
-        <v>14585.19</v>
+        <v>2130.71</v>
       </c>
       <c r="F32" t="s">
-        <v>73</v>
+        <v>188</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>35</v>
-      </c>
-      <c r="B33" t="s">
-        <v>74</v>
+        <v>184</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>267</v>
       </c>
       <c r="C33" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D33" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="E33">
-        <v>7343.63</v>
+        <v>6218.49</v>
       </c>
       <c r="F33" t="s">
-        <v>75</v>
+        <v>268</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>36</v>
-      </c>
-      <c r="B34" t="s">
-        <v>76</v>
+        <v>185</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>269</v>
       </c>
       <c r="C34" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D34" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E34">
-        <v>10928.89</v>
+        <v>2372.5500000000002</v>
       </c>
       <c r="F34" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>37</v>
-      </c>
-      <c r="B35" t="s">
-        <v>78</v>
+        <v>64</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>118</v>
       </c>
       <c r="C35" t="s">
         <v>11</v>
       </c>
       <c r="D35" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E35">
-        <v>15462.28</v>
+        <v>9944.07</v>
       </c>
       <c r="F35" t="s">
-        <v>79</v>
+        <v>119</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>39</v>
-      </c>
-      <c r="B36" t="s">
-        <v>80</v>
+        <v>41</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>83</v>
       </c>
       <c r="C36" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D36" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E36">
-        <v>2811.55</v>
+        <v>18495.95</v>
       </c>
       <c r="F36" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>40</v>
-      </c>
-      <c r="B37" t="s">
-        <v>82</v>
+        <v>86</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>142</v>
       </c>
       <c r="C37" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="D37" t="s">
         <v>30</v>
       </c>
       <c r="E37">
-        <v>16353.44</v>
+        <v>1259.1199999999999</v>
       </c>
       <c r="F37" t="s">
-        <v>47</v>
+        <v>143</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>41</v>
-      </c>
-      <c r="B38" t="s">
-        <v>83</v>
+        <v>23</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="C38" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D38" t="s">
         <v>30</v>
       </c>
       <c r="E38">
-        <v>18495.95</v>
+        <v>12181.89</v>
       </c>
       <c r="F38" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>42</v>
-      </c>
-      <c r="B39" t="s">
-        <v>85</v>
+        <v>175</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>257</v>
       </c>
       <c r="C39" t="s">
         <v>29</v>
       </c>
       <c r="D39" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="E39">
-        <v>15122.3</v>
+        <v>16309.76</v>
       </c>
       <c r="F39" t="s">
-        <v>86</v>
+        <v>258</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>43</v>
-      </c>
-      <c r="B40" t="s">
-        <v>87</v>
+        <v>179</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>250</v>
       </c>
       <c r="C40" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D40" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E40">
-        <v>2217.06</v>
+        <v>9798.56</v>
       </c>
       <c r="F40" t="s">
-        <v>88</v>
+        <v>263</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>44</v>
-      </c>
-      <c r="B41" t="s">
-        <v>89</v>
+        <v>82</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="C41" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D41" t="s">
         <v>30</v>
       </c>
       <c r="E41">
-        <v>14763.4</v>
+        <v>7567.94</v>
       </c>
       <c r="F41" t="s">
-        <v>90</v>
+        <v>137</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>45</v>
-      </c>
-      <c r="B42" t="s">
-        <v>91</v>
+        <v>166</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>246</v>
       </c>
       <c r="C42" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="D42" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E42">
-        <v>1161.79</v>
+        <v>10291.67</v>
       </c>
       <c r="F42" t="s">
-        <v>13</v>
+        <v>102</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>47</v>
-      </c>
-      <c r="B43" t="s">
-        <v>92</v>
+        <v>14</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="C43" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D43" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E43">
-        <v>16620.240000000002</v>
+        <v>10878.01</v>
       </c>
       <c r="F43" t="s">
-        <v>93</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>48</v>
-      </c>
-      <c r="B44" t="s">
-        <v>94</v>
+        <v>162</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>159</v>
       </c>
       <c r="C44" t="s">
         <v>29</v>
@@ -2149,578 +2155,578 @@
         <v>8</v>
       </c>
       <c r="E44">
-        <v>16557.45</v>
+        <v>2465.7600000000002</v>
       </c>
       <c r="F44" t="s">
-        <v>95</v>
+        <v>244</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>50</v>
-      </c>
-      <c r="B45" t="s">
-        <v>96</v>
+        <v>26</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>59</v>
       </c>
       <c r="C45" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D45" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E45">
-        <v>9967.67</v>
+        <v>10062.76</v>
       </c>
       <c r="F45" t="s">
-        <v>97</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>51</v>
-      </c>
-      <c r="B46" t="s">
-        <v>98</v>
+        <v>103</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>170</v>
       </c>
       <c r="C46" t="s">
         <v>11</v>
       </c>
       <c r="D46" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E46">
-        <v>14058.62</v>
+        <v>6249.15</v>
       </c>
       <c r="F46" t="s">
-        <v>99</v>
+        <v>171</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>53</v>
-      </c>
-      <c r="B47" t="s">
-        <v>100</v>
+        <v>85</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>140</v>
       </c>
       <c r="C47" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D47" t="s">
         <v>8</v>
       </c>
       <c r="E47">
-        <v>1544.1</v>
+        <v>5229.25</v>
       </c>
       <c r="F47" t="s">
-        <v>101</v>
+        <v>141</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>54</v>
-      </c>
-      <c r="B48" t="s">
-        <v>57</v>
+        <v>79</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="C48" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D48" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E48">
-        <v>1396.9</v>
+        <v>12485.88</v>
       </c>
       <c r="F48" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>55</v>
-      </c>
-      <c r="B49" t="s">
-        <v>103</v>
+        <v>176</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>195</v>
       </c>
       <c r="C49" t="s">
         <v>7</v>
       </c>
       <c r="D49" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E49">
-        <v>12514.07</v>
+        <v>6071.89</v>
       </c>
       <c r="F49" t="s">
-        <v>104</v>
+        <v>259</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>57</v>
-      </c>
-      <c r="B50" t="s">
-        <v>105</v>
+        <v>167</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>247</v>
       </c>
       <c r="C50" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D50" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E50">
-        <v>2580.04</v>
+        <v>15065.96</v>
       </c>
       <c r="F50" t="s">
-        <v>106</v>
+        <v>248</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>58</v>
-      </c>
-      <c r="B51" t="s">
-        <v>107</v>
+        <v>159</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>236</v>
       </c>
       <c r="C51" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D51" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E51">
-        <v>10157.530000000001</v>
+        <v>8751.02</v>
       </c>
       <c r="F51" t="s">
-        <v>108</v>
+        <v>239</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>59</v>
-      </c>
-      <c r="B52" t="s">
-        <v>109</v>
+        <v>13</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="C52" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="D52" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E52">
-        <v>9420.8700000000008</v>
+        <v>15504.96</v>
       </c>
       <c r="F52" t="s">
-        <v>110</v>
+        <v>40</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>60</v>
-      </c>
-      <c r="B53" t="s">
-        <v>111</v>
+        <v>7</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="C53" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D53" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E53">
-        <v>190090</v>
+        <v>12713.59</v>
       </c>
       <c r="F53" t="s">
-        <v>112</v>
+        <v>27</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>61</v>
-      </c>
-      <c r="B54" t="s">
-        <v>113</v>
+        <v>47</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="C54" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D54" t="s">
         <v>8</v>
       </c>
       <c r="E54">
-        <v>7465.38</v>
+        <v>16620.240000000002</v>
       </c>
       <c r="F54" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>62</v>
-      </c>
-      <c r="B55" t="s">
-        <v>115</v>
+        <v>1</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="C55" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D55" t="s">
         <v>8</v>
       </c>
       <c r="E55">
-        <v>5058.54</v>
+        <v>11670.1</v>
       </c>
       <c r="F55" t="s">
-        <v>116</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>63</v>
-      </c>
-      <c r="B56" t="s">
-        <v>117</v>
+        <v>3</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C56" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="D56" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E56">
-        <v>14912.48</v>
+        <v>19787.46</v>
       </c>
       <c r="F56" t="s">
-        <v>90</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>64</v>
-      </c>
-      <c r="B57" t="s">
-        <v>118</v>
+        <v>62</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>115</v>
       </c>
       <c r="C57" t="s">
         <v>11</v>
       </c>
       <c r="D57" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E57">
-        <v>9944.07</v>
+        <v>5058.54</v>
       </c>
       <c r="F57" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>65</v>
-      </c>
-      <c r="B58" t="s">
-        <v>57</v>
+        <v>130</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="C58" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D58" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E58">
-        <v>11993.61</v>
+        <v>14398.71</v>
       </c>
       <c r="F58" t="s">
-        <v>120</v>
+        <v>206</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>66</v>
-      </c>
-      <c r="B59" t="s">
-        <v>121</v>
+        <v>48</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>94</v>
       </c>
       <c r="C59" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D59" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E59">
-        <v>12754.6</v>
+        <v>16557.45</v>
       </c>
       <c r="F59" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>67</v>
-      </c>
-      <c r="B60" t="s">
-        <v>123</v>
+        <v>169</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>94</v>
       </c>
       <c r="C60" t="s">
         <v>29</v>
       </c>
       <c r="D60" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E60">
-        <v>11939.42</v>
+        <v>16451.39</v>
       </c>
       <c r="F60" t="s">
-        <v>124</v>
+        <v>249</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>68</v>
-      </c>
-      <c r="B61" t="s">
-        <v>125</v>
+        <v>45</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="C61" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D61" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E61">
-        <v>45438.400000000001</v>
+        <v>1161.79</v>
       </c>
       <c r="F61" t="s">
-        <v>79</v>
+        <v>13</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>69</v>
-      </c>
-      <c r="B62" t="s">
-        <v>126</v>
+        <v>32</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="C62" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D62" t="s">
         <v>8</v>
       </c>
       <c r="E62">
-        <v>15100.76</v>
+        <v>570.52</v>
       </c>
       <c r="F62" t="s">
-        <v>114</v>
+        <v>69</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>70</v>
-      </c>
-      <c r="B63" t="s">
-        <v>127</v>
+        <v>24</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="C63" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D63" t="s">
         <v>8</v>
       </c>
       <c r="E63">
-        <v>9473.7099999999991</v>
+        <v>8180.55</v>
       </c>
       <c r="F63" t="s">
-        <v>128</v>
+        <v>33</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>71</v>
-      </c>
-      <c r="B64" t="s">
-        <v>125</v>
+        <v>150</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>227</v>
       </c>
       <c r="C64" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D64" t="s">
         <v>8</v>
       </c>
       <c r="E64">
-        <v>11648.28</v>
+        <v>1323.87</v>
       </c>
       <c r="F64" t="s">
-        <v>129</v>
+        <v>93</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>73</v>
-      </c>
-      <c r="B65" t="s">
-        <v>103</v>
+        <v>12</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="C65" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D65" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E65">
-        <v>124.41</v>
+        <v>14020.35</v>
       </c>
       <c r="F65" t="s">
-        <v>130</v>
+        <v>38</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>76</v>
-      </c>
-      <c r="B66" t="s">
-        <v>115</v>
+        <v>198</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>289</v>
       </c>
       <c r="C66" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D66" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E66">
-        <v>13833.9</v>
+        <v>12795.28</v>
       </c>
       <c r="F66" t="s">
-        <v>131</v>
+        <v>290</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67">
-        <v>77</v>
-      </c>
-      <c r="B67" t="s">
-        <v>132</v>
+        <v>71</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="C67" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D67" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E67">
-        <v>14771.55</v>
+        <v>11648.28</v>
       </c>
       <c r="F67" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>78</v>
-      </c>
-      <c r="B68" t="s">
-        <v>134</v>
+        <v>93</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>152</v>
       </c>
       <c r="C68" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D68" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E68">
-        <v>12378.33</v>
+        <v>4389.2</v>
       </c>
       <c r="F68" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>79</v>
-      </c>
-      <c r="B69" t="s">
-        <v>32</v>
+        <v>37</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="C69" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D69" t="s">
         <v>8</v>
       </c>
       <c r="E69">
-        <v>12485.88</v>
+        <v>15462.28</v>
       </c>
       <c r="F69" t="s">
-        <v>136</v>
+        <v>79</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70">
-        <v>80</v>
-      </c>
-      <c r="B70" t="s">
-        <v>89</v>
+        <v>153</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>231</v>
       </c>
       <c r="C70" t="s">
         <v>11</v>
       </c>
       <c r="D70" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E70">
-        <v>15302.57</v>
+        <v>73.13</v>
       </c>
       <c r="F70" t="s">
-        <v>101</v>
+        <v>40</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71">
-        <v>82</v>
-      </c>
-      <c r="B71" t="s">
-        <v>70</v>
+        <v>108</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>177</v>
       </c>
       <c r="C71" t="s">
         <v>11</v>
       </c>
       <c r="D71" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E71">
-        <v>7567.94</v>
+        <v>14151.6</v>
       </c>
       <c r="F71" t="s">
-        <v>137</v>
+        <v>178</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72">
-        <v>83</v>
-      </c>
-      <c r="B72" t="s">
-        <v>138</v>
+        <v>178</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D72" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E72">
-        <v>4637.51</v>
+        <v>5194.28</v>
       </c>
       <c r="F72" t="s">
-        <v>139</v>
+        <v>262</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73">
-        <v>85</v>
-      </c>
-      <c r="B73" t="s">
-        <v>140</v>
+        <v>10</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="C73" t="s">
         <v>7</v>
@@ -2729,598 +2735,598 @@
         <v>8</v>
       </c>
       <c r="E73">
-        <v>5229.25</v>
+        <v>10511.56</v>
       </c>
       <c r="F73" t="s">
-        <v>141</v>
+        <v>35</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74">
-        <v>86</v>
-      </c>
-      <c r="B74" t="s">
-        <v>142</v>
+        <v>109</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>179</v>
       </c>
       <c r="C74" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D74" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E74">
-        <v>1259.1199999999999</v>
+        <v>11835.53</v>
       </c>
       <c r="F74" t="s">
-        <v>143</v>
+        <v>75</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75">
-        <v>87</v>
-      </c>
-      <c r="B75" t="s">
-        <v>144</v>
+        <v>36</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="C75" t="s">
         <v>11</v>
       </c>
       <c r="D75" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E75">
-        <v>18061.419999999998</v>
+        <v>10928.89</v>
       </c>
       <c r="F75" t="s">
-        <v>145</v>
+        <v>77</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76">
-        <v>88</v>
-      </c>
-      <c r="B76" t="s">
-        <v>146</v>
+        <v>69</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>126</v>
       </c>
       <c r="C76" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D76" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E76">
-        <v>1017.03</v>
+        <v>15100.76</v>
       </c>
       <c r="F76" t="s">
-        <v>147</v>
+        <v>114</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77">
-        <v>89</v>
-      </c>
-      <c r="B77" t="s">
-        <v>148</v>
+        <v>43</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="C77" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D77" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E77">
-        <v>12768</v>
+        <v>2217.06</v>
       </c>
       <c r="F77" t="s">
-        <v>149</v>
+        <v>88</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78">
-        <v>90</v>
-      </c>
-      <c r="B78" t="s">
-        <v>150</v>
+        <v>61</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>113</v>
       </c>
       <c r="C78" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D78" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E78">
-        <v>17475.57</v>
+        <v>7465.38</v>
       </c>
       <c r="F78" t="s">
-        <v>151</v>
+        <v>114</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79">
-        <v>93</v>
-      </c>
-      <c r="B79" t="s">
-        <v>152</v>
+        <v>53</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="C79" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D79" t="s">
         <v>8</v>
       </c>
       <c r="E79">
-        <v>4389.2</v>
+        <v>1544.1</v>
       </c>
       <c r="F79" t="s">
-        <v>153</v>
+        <v>101</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80">
-        <v>94</v>
-      </c>
-      <c r="B80" t="s">
-        <v>154</v>
+        <v>143</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>218</v>
       </c>
       <c r="C80" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="D80" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E80">
-        <v>6312.57</v>
+        <v>6803.42</v>
       </c>
       <c r="F80" t="s">
-        <v>155</v>
+        <v>200</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81">
-        <v>95</v>
-      </c>
-      <c r="B81" t="s">
-        <v>156</v>
+        <v>194</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>154</v>
       </c>
       <c r="C81" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="D81" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E81">
-        <v>15524</v>
+        <v>2275.15</v>
       </c>
       <c r="F81" t="s">
-        <v>157</v>
+        <v>282</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82">
-        <v>96</v>
-      </c>
-      <c r="B82" t="s">
-        <v>32</v>
+        <v>139</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>214</v>
       </c>
       <c r="C82" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D82" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E82">
-        <v>1221.3800000000001</v>
+        <v>16028.2</v>
       </c>
       <c r="F82" t="s">
-        <v>158</v>
+        <v>215</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83">
-        <v>97</v>
-      </c>
-      <c r="B83" t="s">
-        <v>159</v>
+        <v>70</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>127</v>
       </c>
       <c r="C83" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D83" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E83">
-        <v>11497</v>
+        <v>9473.7099999999991</v>
       </c>
       <c r="F83" t="s">
-        <v>160</v>
+        <v>128</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84">
-        <v>98</v>
-      </c>
-      <c r="B84" t="s">
-        <v>117</v>
+        <v>183</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>266</v>
       </c>
       <c r="C84" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D84" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E84">
-        <v>16618.39</v>
+        <v>2345.2800000000002</v>
       </c>
       <c r="F84" t="s">
-        <v>161</v>
+        <v>216</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85">
-        <v>99</v>
-      </c>
-      <c r="B85" t="s">
-        <v>162</v>
+        <v>106</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>173</v>
       </c>
       <c r="C85" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D85" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E85">
-        <v>1478.93</v>
+        <v>17022</v>
       </c>
       <c r="F85" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86">
-        <v>100</v>
-      </c>
-      <c r="B86" t="s">
-        <v>164</v>
+        <v>97</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>159</v>
       </c>
       <c r="C86" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D86" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E86">
-        <v>8574.59</v>
+        <v>11497</v>
       </c>
       <c r="F86" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87">
-        <v>101</v>
-      </c>
-      <c r="B87" t="s">
-        <v>166</v>
+        <v>182</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>265</v>
       </c>
       <c r="C87" t="s">
         <v>21</v>
       </c>
       <c r="D87" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E87">
-        <v>4267.79</v>
+        <v>3003.23</v>
       </c>
       <c r="F87" t="s">
-        <v>167</v>
+        <v>201</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88">
-        <v>102</v>
-      </c>
-      <c r="B88" t="s">
-        <v>168</v>
+        <v>118</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>192</v>
       </c>
       <c r="C88" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D88" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E88">
-        <v>10186.549999999999</v>
+        <v>8827.6200000000008</v>
       </c>
       <c r="F88" t="s">
-        <v>169</v>
+        <v>40</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89">
-        <v>103</v>
-      </c>
-      <c r="B89" t="s">
-        <v>170</v>
+        <v>131</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>197</v>
       </c>
       <c r="C89" t="s">
         <v>11</v>
       </c>
       <c r="D89" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E89">
-        <v>6249.15</v>
+        <v>19582.169999999998</v>
       </c>
       <c r="F89" t="s">
-        <v>171</v>
+        <v>119</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90">
-        <v>104</v>
-      </c>
-      <c r="B90" t="s">
-        <v>164</v>
+        <v>149</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>134</v>
       </c>
       <c r="C90" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D90" t="s">
         <v>12</v>
       </c>
       <c r="E90">
-        <v>13418.44</v>
+        <v>10273.799999999999</v>
       </c>
       <c r="F90" t="s">
-        <v>47</v>
+        <v>226</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91">
-        <v>105</v>
-      </c>
-      <c r="B91" t="s">
-        <v>172</v>
+        <v>174</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>247</v>
       </c>
       <c r="C91" t="s">
         <v>11</v>
       </c>
       <c r="D91" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E91">
-        <v>2839.29</v>
+        <v>3773.75</v>
       </c>
       <c r="F91" t="s">
-        <v>112</v>
+        <v>256</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92">
-        <v>106</v>
-      </c>
-      <c r="B92" t="s">
-        <v>173</v>
+        <v>50</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="C92" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="D92" t="s">
         <v>12</v>
       </c>
       <c r="E92">
-        <v>17022</v>
+        <v>9967.67</v>
       </c>
       <c r="F92" t="s">
-        <v>174</v>
+        <v>97</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93">
-        <v>107</v>
-      </c>
-      <c r="B93" t="s">
-        <v>175</v>
+        <v>88</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>146</v>
       </c>
       <c r="C93" t="s">
         <v>17</v>
       </c>
       <c r="D93" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E93">
-        <v>110.25</v>
+        <v>1017.03</v>
       </c>
       <c r="F93" t="s">
-        <v>176</v>
+        <v>147</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94">
-        <v>108</v>
-      </c>
-      <c r="B94" t="s">
-        <v>177</v>
+        <v>199</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>291</v>
       </c>
       <c r="C94" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D94" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E94">
-        <v>14151.6</v>
+        <v>9634.17</v>
       </c>
       <c r="F94" t="s">
-        <v>178</v>
+        <v>292</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95">
-        <v>109</v>
-      </c>
-      <c r="B95" t="s">
-        <v>179</v>
+        <v>51</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="C95" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D95" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E95">
-        <v>11835.53</v>
+        <v>14058.62</v>
       </c>
       <c r="F95" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96">
-        <v>111</v>
-      </c>
-      <c r="B96" t="s">
-        <v>180</v>
+        <v>164</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="C96" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D96" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E96">
-        <v>3302.72</v>
+        <v>13777.95</v>
       </c>
       <c r="F96" t="s">
-        <v>181</v>
+        <v>60</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97">
-        <v>112</v>
-      </c>
-      <c r="B97" t="s">
-        <v>182</v>
+        <v>98</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>117</v>
       </c>
       <c r="C97" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D97" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E97">
-        <v>2490.62</v>
+        <v>16618.39</v>
       </c>
       <c r="F97" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98">
-        <v>113</v>
-      </c>
-      <c r="B98" t="s">
-        <v>184</v>
+        <v>2</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="C98" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D98" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E98">
-        <v>1124.9100000000001</v>
+        <v>17394.82</v>
       </c>
       <c r="F98" t="s">
-        <v>185</v>
+        <v>13</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99">
-        <v>114</v>
-      </c>
-      <c r="B99" t="s">
-        <v>74</v>
+        <v>128</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>202</v>
       </c>
       <c r="C99" t="s">
         <v>11</v>
       </c>
       <c r="D99" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E99">
-        <v>11116.96</v>
+        <v>10079.33</v>
       </c>
       <c r="F99" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100">
-        <v>115</v>
-      </c>
-      <c r="B100" t="s">
-        <v>187</v>
+        <v>65</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>57</v>
       </c>
       <c r="C100" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D100" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="E100">
-        <v>2130.71</v>
+        <v>11993.61</v>
       </c>
       <c r="F100" t="s">
-        <v>188</v>
+        <v>120</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101">
-        <v>116</v>
-      </c>
-      <c r="B101" t="s">
-        <v>189</v>
+        <v>127</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="C101" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D101" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E101">
-        <v>17243.939999999999</v>
+        <v>39788.699999999997</v>
       </c>
       <c r="F101" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102">
-        <v>117</v>
-      </c>
-      <c r="B102" t="s">
-        <v>191</v>
+        <v>104</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>164</v>
       </c>
       <c r="C102" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D102" t="s">
         <v>12</v>
       </c>
       <c r="E102">
-        <v>8964.76</v>
+        <v>13418.44</v>
       </c>
       <c r="F102" t="s">
-        <v>149</v>
+        <v>47</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103">
-        <v>118</v>
-      </c>
-      <c r="B103" t="s">
-        <v>192</v>
+        <v>180</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>152</v>
       </c>
       <c r="C103" t="s">
         <v>21</v>
@@ -3329,118 +3335,118 @@
         <v>12</v>
       </c>
       <c r="E103">
-        <v>8827.6200000000008</v>
+        <v>6962.14</v>
       </c>
       <c r="F103" t="s">
-        <v>40</v>
+        <v>264</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104">
-        <v>119</v>
-      </c>
-      <c r="B104" t="s">
-        <v>193</v>
+        <v>155</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>232</v>
       </c>
       <c r="C104" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D104" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E104">
-        <v>3908.4</v>
+        <v>9150.0499999999993</v>
       </c>
       <c r="F104" t="s">
-        <v>194</v>
+        <v>233</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105">
-        <v>121</v>
-      </c>
-      <c r="B105" t="s">
-        <v>195</v>
+        <v>87</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="C105" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D105" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="E105">
-        <v>16317.04</v>
+        <v>18061.419999999998</v>
       </c>
       <c r="F105" t="s">
-        <v>196</v>
+        <v>145</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106">
-        <v>122</v>
-      </c>
-      <c r="B106" t="s">
-        <v>197</v>
+        <v>42</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="C106" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D106" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E106">
-        <v>6990.84</v>
+        <v>15122.3</v>
       </c>
       <c r="F106" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107">
-        <v>125</v>
-      </c>
-      <c r="B107" t="s">
-        <v>198</v>
+        <v>11</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="C107" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D107" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E107">
-        <v>8845.4</v>
+        <v>14855</v>
       </c>
       <c r="F107" t="s">
-        <v>190</v>
+        <v>33</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108">
-        <v>126</v>
-      </c>
-      <c r="B108" t="s">
-        <v>199</v>
+        <v>28</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="C108" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D108" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E108">
-        <v>15974.01</v>
+        <v>16226.08</v>
       </c>
       <c r="F108" t="s">
-        <v>200</v>
+        <v>38</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109">
-        <v>127</v>
-      </c>
-      <c r="B109" t="s">
-        <v>37</v>
+        <v>35</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>74</v>
       </c>
       <c r="C109" t="s">
         <v>29</v>
@@ -3449,1218 +3455,1218 @@
         <v>12</v>
       </c>
       <c r="E109">
-        <v>39788.699999999997</v>
+        <v>7343.63</v>
       </c>
       <c r="F109" t="s">
-        <v>201</v>
+        <v>75</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110">
-        <v>128</v>
-      </c>
-      <c r="B110" t="s">
-        <v>202</v>
+        <v>34</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>72</v>
       </c>
       <c r="C110" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D110" t="s">
         <v>12</v>
       </c>
       <c r="E110">
-        <v>10079.33</v>
+        <v>14585.19</v>
       </c>
       <c r="F110" t="s">
-        <v>203</v>
+        <v>73</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111">
-        <v>129</v>
-      </c>
-      <c r="B111" t="s">
-        <v>204</v>
+        <v>117</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>191</v>
       </c>
       <c r="C111" t="s">
         <v>21</v>
       </c>
       <c r="D111" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="E111">
-        <v>2048.67</v>
+        <v>8964.76</v>
       </c>
       <c r="F111" t="s">
-        <v>205</v>
+        <v>149</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112">
-        <v>130</v>
-      </c>
-      <c r="B112" t="s">
-        <v>16</v>
+        <v>188</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>274</v>
       </c>
       <c r="C112" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="D112" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E112">
-        <v>14398.71</v>
+        <v>19110.080000000002</v>
       </c>
       <c r="F112" t="s">
-        <v>206</v>
+        <v>275</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113">
-        <v>131</v>
-      </c>
-      <c r="B113" t="s">
-        <v>197</v>
+        <v>171</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>250</v>
       </c>
       <c r="C113" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="D113" t="s">
         <v>12</v>
       </c>
       <c r="E113">
-        <v>19582.169999999998</v>
+        <v>965.46</v>
       </c>
       <c r="F113" t="s">
-        <v>119</v>
+        <v>251</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114">
-        <v>132</v>
-      </c>
-      <c r="B114" t="s">
-        <v>207</v>
+        <v>89</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>148</v>
       </c>
       <c r="C114" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="D114" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E114">
-        <v>10108.25</v>
+        <v>12768</v>
       </c>
       <c r="F114" t="s">
-        <v>208</v>
+        <v>149</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115">
-        <v>133</v>
-      </c>
-      <c r="B115" t="s">
-        <v>138</v>
+        <v>33</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="C115" t="s">
         <v>21</v>
       </c>
       <c r="D115" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E115">
-        <v>5593.16</v>
+        <v>17704.330000000002</v>
       </c>
       <c r="F115" t="s">
-        <v>209</v>
+        <v>71</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116">
-        <v>134</v>
-      </c>
-      <c r="B116" t="s">
-        <v>62</v>
+        <v>145</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>220</v>
       </c>
       <c r="C116" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D116" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E116">
-        <v>9888.43</v>
+        <v>17949.97</v>
       </c>
       <c r="F116" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117">
-        <v>136</v>
-      </c>
-      <c r="B117" t="s">
-        <v>100</v>
+        <v>9</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="C117" t="s">
         <v>29</v>
       </c>
       <c r="D117" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E117">
-        <v>8073.66</v>
+        <v>398.2</v>
       </c>
       <c r="F117" t="s">
-        <v>211</v>
+        <v>33</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118">
-        <v>137</v>
-      </c>
-      <c r="B118" t="s">
-        <v>212</v>
+        <v>96</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="C118" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D118" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E118">
-        <v>6052.29</v>
+        <v>1221.3800000000001</v>
       </c>
       <c r="F118" t="s">
-        <v>40</v>
+        <v>158</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119">
-        <v>138</v>
-      </c>
-      <c r="B119" t="s">
-        <v>177</v>
+        <v>29</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="C119" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D119" t="s">
         <v>18</v>
       </c>
       <c r="E119">
-        <v>18719.07</v>
+        <v>18045.12</v>
       </c>
       <c r="F119" t="s">
-        <v>213</v>
+        <v>63</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120">
-        <v>139</v>
-      </c>
-      <c r="B120" t="s">
-        <v>214</v>
+        <v>158</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>238</v>
       </c>
       <c r="C120" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="D120" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E120">
-        <v>16028.2</v>
+        <v>9099.5400000000009</v>
       </c>
       <c r="F120" t="s">
-        <v>215</v>
+        <v>33</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121">
-        <v>141</v>
-      </c>
-      <c r="B121" t="s">
-        <v>100</v>
+        <v>39</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>80</v>
       </c>
       <c r="C121" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D121" t="s">
         <v>18</v>
       </c>
       <c r="E121">
-        <v>17633.259999999998</v>
+        <v>2811.55</v>
       </c>
       <c r="F121" t="s">
-        <v>216</v>
+        <v>81</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122">
-        <v>142</v>
-      </c>
-      <c r="B122" t="s">
-        <v>217</v>
+        <v>101</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>166</v>
       </c>
       <c r="C122" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D122" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E122">
-        <v>103679.4</v>
+        <v>4267.79</v>
       </c>
       <c r="F122" t="s">
-        <v>45</v>
+        <v>167</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123">
-        <v>143</v>
-      </c>
-      <c r="B123" t="s">
-        <v>218</v>
+        <v>4</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="C123" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D123" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E123">
-        <v>6803.42</v>
+        <v>2159.77</v>
       </c>
       <c r="F123" t="s">
-        <v>200</v>
+        <v>19</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124">
-        <v>144</v>
-      </c>
-      <c r="B124" t="s">
-        <v>191</v>
+        <v>18</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="C124" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D124" t="s">
         <v>18</v>
       </c>
       <c r="E124">
-        <v>19363.099999999999</v>
+        <v>15605.07</v>
       </c>
       <c r="F124" t="s">
-        <v>219</v>
+        <v>45</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125">
-        <v>145</v>
-      </c>
-      <c r="B125" t="s">
-        <v>220</v>
+        <v>112</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>182</v>
       </c>
       <c r="C125" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="D125" t="s">
         <v>18</v>
       </c>
       <c r="E125">
-        <v>17949.97</v>
+        <v>2490.62</v>
       </c>
       <c r="F125" t="s">
-        <v>221</v>
+        <v>183</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126">
-        <v>146</v>
-      </c>
-      <c r="B126" t="s">
-        <v>222</v>
+        <v>196</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>285</v>
       </c>
       <c r="C126" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="D126" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E126">
-        <v>12982.56</v>
+        <v>15225.1</v>
       </c>
       <c r="F126" t="s">
-        <v>13</v>
+        <v>286</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127">
-        <v>147</v>
-      </c>
-      <c r="B127" t="s">
-        <v>223</v>
+        <v>119</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>193</v>
       </c>
       <c r="C127" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D127" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E127">
-        <v>18391.28</v>
+        <v>3908.4</v>
       </c>
       <c r="F127" t="s">
-        <v>149</v>
+        <v>194</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128">
-        <v>148</v>
-      </c>
-      <c r="B128" t="s">
-        <v>224</v>
+        <v>100</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>164</v>
       </c>
       <c r="C128" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D128" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E128">
-        <v>101064.7</v>
+        <v>8574.59</v>
       </c>
       <c r="F128" t="s">
-        <v>225</v>
+        <v>165</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129">
-        <v>149</v>
-      </c>
-      <c r="B129" t="s">
-        <v>134</v>
+        <v>111</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>180</v>
       </c>
       <c r="C129" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D129" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E129">
-        <v>10273.799999999999</v>
+        <v>3302.72</v>
       </c>
       <c r="F129" t="s">
-        <v>226</v>
+        <v>181</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130">
-        <v>150</v>
-      </c>
-      <c r="B130" t="s">
-        <v>227</v>
+        <v>138</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>177</v>
       </c>
       <c r="C130" t="s">
         <v>11</v>
       </c>
       <c r="D130" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E130">
-        <v>1323.87</v>
+        <v>18719.07</v>
       </c>
       <c r="F130" t="s">
-        <v>93</v>
+        <v>213</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131">
-        <v>151</v>
-      </c>
-      <c r="B131" t="s">
-        <v>228</v>
+        <v>58</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>107</v>
       </c>
       <c r="C131" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D131" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E131">
-        <v>11345.68</v>
+        <v>10157.530000000001</v>
       </c>
       <c r="F131" t="s">
-        <v>229</v>
+        <v>108</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132">
-        <v>152</v>
-      </c>
-      <c r="B132" t="s">
-        <v>230</v>
+        <v>15</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="C132" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="D132" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E132">
-        <v>12213.03</v>
+        <v>6450.78</v>
       </c>
       <c r="F132" t="s">
-        <v>149</v>
+        <v>43</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133">
-        <v>153</v>
-      </c>
-      <c r="B133" t="s">
-        <v>231</v>
+        <v>80</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="C133" t="s">
         <v>11</v>
       </c>
       <c r="D133" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E133">
-        <v>73.13</v>
+        <v>15302.57</v>
       </c>
       <c r="F133" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134">
-        <v>155</v>
-      </c>
-      <c r="B134" t="s">
-        <v>232</v>
+        <v>186</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>270</v>
       </c>
       <c r="C134" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D134" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E134">
-        <v>9150.0499999999993</v>
+        <v>1536.6</v>
       </c>
       <c r="F134" t="s">
-        <v>233</v>
+        <v>271</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135">
-        <v>156</v>
-      </c>
-      <c r="B135" t="s">
-        <v>234</v>
+        <v>83</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>138</v>
       </c>
       <c r="C135" t="s">
         <v>29</v>
       </c>
       <c r="D135" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E135">
-        <v>16694.14</v>
+        <v>4637.51</v>
       </c>
       <c r="F135" t="s">
-        <v>235</v>
+        <v>139</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136">
-        <v>157</v>
-      </c>
-      <c r="B136" t="s">
-        <v>236</v>
+        <v>114</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>74</v>
       </c>
       <c r="C136" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D136" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E136">
-        <v>5352.15</v>
+        <v>11116.96</v>
       </c>
       <c r="F136" t="s">
-        <v>237</v>
+        <v>186</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137">
-        <v>158</v>
-      </c>
-      <c r="B137" t="s">
-        <v>238</v>
+        <v>200</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="C137" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="D137" t="s">
         <v>18</v>
       </c>
       <c r="E137">
-        <v>9099.5400000000009</v>
+        <v>13022</v>
       </c>
       <c r="F137" t="s">
-        <v>33</v>
+        <v>293</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138">
-        <v>159</v>
-      </c>
-      <c r="B138" t="s">
-        <v>236</v>
+        <v>161</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>242</v>
       </c>
       <c r="C138" t="s">
         <v>29</v>
       </c>
       <c r="D138" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E138">
-        <v>8751.02</v>
+        <v>96075.5</v>
       </c>
       <c r="F138" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139">
-        <v>160</v>
-      </c>
-      <c r="B139" t="s">
-        <v>240</v>
+        <v>144</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>191</v>
       </c>
       <c r="C139" t="s">
         <v>11</v>
       </c>
       <c r="D139" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E139">
-        <v>1884.31</v>
+        <v>19363.099999999999</v>
       </c>
       <c r="F139" t="s">
-        <v>241</v>
+        <v>219</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140">
-        <v>161</v>
-      </c>
-      <c r="B140" t="s">
-        <v>242</v>
+        <v>125</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>198</v>
       </c>
       <c r="C140" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="D140" t="s">
         <v>18</v>
       </c>
       <c r="E140">
-        <v>96075.5</v>
+        <v>8845.4</v>
       </c>
       <c r="F140" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141">
-        <v>162</v>
-      </c>
-      <c r="B141" t="s">
-        <v>159</v>
+        <v>141</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="C141" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D141" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E141">
-        <v>2465.7600000000002</v>
+        <v>17633.259999999998</v>
       </c>
       <c r="F141" t="s">
-        <v>244</v>
+        <v>216</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142">
-        <v>163</v>
-      </c>
-      <c r="B142" t="s">
-        <v>238</v>
+        <v>189</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>276</v>
       </c>
       <c r="C142" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D142" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E142">
-        <v>12551.21</v>
+        <v>11426.16</v>
       </c>
       <c r="F142" t="s">
-        <v>47</v>
+        <v>277</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143">
-        <v>164</v>
-      </c>
-      <c r="B143" t="s">
-        <v>44</v>
+        <v>55</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="C143" t="s">
         <v>7</v>
       </c>
       <c r="D143" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E143">
-        <v>13777.95</v>
+        <v>12514.07</v>
       </c>
       <c r="F143" t="s">
-        <v>60</v>
+        <v>104</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144">
-        <v>165</v>
-      </c>
-      <c r="B144" t="s">
-        <v>245</v>
+        <v>21</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="C144" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D144" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E144">
-        <v>12352.28</v>
+        <v>814.96</v>
       </c>
       <c r="F144" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145">
-        <v>166</v>
-      </c>
-      <c r="B145" t="s">
-        <v>246</v>
+        <v>126</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>199</v>
       </c>
       <c r="C145" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="D145" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E145">
-        <v>10291.67</v>
+        <v>15974.01</v>
       </c>
       <c r="F145" t="s">
-        <v>102</v>
+        <v>200</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146">
-        <v>167</v>
-      </c>
-      <c r="B146" t="s">
-        <v>247</v>
+        <v>19</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="C146" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="D146" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E146">
-        <v>15065.96</v>
+        <v>11327.78</v>
       </c>
       <c r="F146" t="s">
-        <v>248</v>
+        <v>47</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147">
-        <v>169</v>
-      </c>
-      <c r="B147" t="s">
-        <v>94</v>
+        <v>156</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>234</v>
       </c>
       <c r="C147" t="s">
         <v>29</v>
       </c>
       <c r="D147" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E147">
-        <v>16451.39</v>
+        <v>16694.14</v>
       </c>
       <c r="F147" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148">
-        <v>171</v>
-      </c>
-      <c r="B148" t="s">
-        <v>250</v>
+        <v>142</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>217</v>
       </c>
       <c r="C148" t="s">
         <v>29</v>
       </c>
       <c r="D148" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E148">
-        <v>965.46</v>
+        <v>103679.4</v>
       </c>
       <c r="F148" t="s">
-        <v>251</v>
+        <v>45</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149">
-        <v>172</v>
-      </c>
-      <c r="B149" t="s">
-        <v>252</v>
+        <v>177</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>260</v>
       </c>
       <c r="C149" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D149" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E149">
-        <v>14432.77</v>
+        <v>12306.04</v>
       </c>
       <c r="F149" t="s">
-        <v>253</v>
+        <v>213</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150">
-        <v>173</v>
-      </c>
-      <c r="B150" t="s">
-        <v>254</v>
+        <v>107</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>175</v>
       </c>
       <c r="C150" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D150" t="s">
         <v>22</v>
       </c>
       <c r="E150">
-        <v>15566.04</v>
+        <v>110.25</v>
       </c>
       <c r="F150" t="s">
-        <v>255</v>
+        <v>176</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151">
-        <v>174</v>
-      </c>
-      <c r="B151" t="s">
-        <v>247</v>
+        <v>122</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>197</v>
       </c>
       <c r="C151" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D151" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E151">
-        <v>3773.75</v>
+        <v>6990.84</v>
       </c>
       <c r="F151" t="s">
-        <v>256</v>
+        <v>102</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152">
-        <v>175</v>
-      </c>
-      <c r="B152" t="s">
-        <v>257</v>
+        <v>134</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="C152" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D152" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E152">
-        <v>16309.76</v>
+        <v>9888.43</v>
       </c>
       <c r="F152" t="s">
-        <v>258</v>
+        <v>210</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153">
-        <v>176</v>
-      </c>
-      <c r="B153" t="s">
-        <v>195</v>
+        <v>22</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="C153" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="D153" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E153">
-        <v>6071.89</v>
+        <v>7317.09</v>
       </c>
       <c r="F153" t="s">
-        <v>259</v>
+        <v>53</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154">
-        <v>177</v>
-      </c>
-      <c r="B154" t="s">
-        <v>260</v>
+        <v>197</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>287</v>
       </c>
       <c r="C154" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D154" t="s">
         <v>22</v>
       </c>
       <c r="E154">
-        <v>12306.04</v>
+        <v>16460.68</v>
       </c>
       <c r="F154" t="s">
-        <v>213</v>
+        <v>288</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155">
-        <v>178</v>
-      </c>
-      <c r="B155" t="s">
-        <v>261</v>
+        <v>165</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="C155" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D155" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E155">
-        <v>5194.28</v>
+        <v>12352.28</v>
       </c>
       <c r="F155" t="s">
-        <v>262</v>
+        <v>13</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156">
-        <v>179</v>
-      </c>
-      <c r="B156" t="s">
-        <v>250</v>
+        <v>137</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>212</v>
       </c>
       <c r="C156" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="D156" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E156">
-        <v>9798.56</v>
+        <v>6052.29</v>
       </c>
       <c r="F156" t="s">
-        <v>263</v>
+        <v>40</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157">
-        <v>180</v>
-      </c>
-      <c r="B157" t="s">
-        <v>152</v>
+        <v>195</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>283</v>
       </c>
       <c r="C157" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D157" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E157">
-        <v>6962.14</v>
+        <v>18170.310000000001</v>
       </c>
       <c r="F157" t="s">
-        <v>264</v>
+        <v>284</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158">
-        <v>182</v>
-      </c>
-      <c r="B158" t="s">
-        <v>265</v>
+        <v>76</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>115</v>
       </c>
       <c r="C158" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D158" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E158">
-        <v>3003.23</v>
+        <v>13833.9</v>
       </c>
       <c r="F158" t="s">
-        <v>201</v>
+        <v>131</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A159">
-        <v>183</v>
-      </c>
-      <c r="B159" t="s">
-        <v>266</v>
+        <v>132</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="C159" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="D159" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E159">
-        <v>2345.2800000000002</v>
+        <v>10108.25</v>
       </c>
       <c r="F159" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160">
-        <v>184</v>
-      </c>
-      <c r="B160" t="s">
-        <v>267</v>
+        <v>105</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="C160" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D160" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E160">
-        <v>6218.49</v>
+        <v>2839.29</v>
       </c>
       <c r="F160" t="s">
-        <v>268</v>
+        <v>112</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161">
-        <v>185</v>
-      </c>
-      <c r="B161" t="s">
-        <v>269</v>
+        <v>66</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>121</v>
       </c>
       <c r="C161" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D161" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E161">
-        <v>2372.5500000000002</v>
+        <v>12754.6</v>
       </c>
       <c r="F161" t="s">
-        <v>42</v>
+        <v>122</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A162">
-        <v>186</v>
-      </c>
-      <c r="B162" t="s">
-        <v>270</v>
+        <v>25</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>57</v>
       </c>
       <c r="C162" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D162" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E162">
-        <v>1536.6</v>
+        <v>13129.43</v>
       </c>
       <c r="F162" t="s">
-        <v>271</v>
+        <v>58</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163">
-        <v>187</v>
-      </c>
-      <c r="B163" t="s">
-        <v>272</v>
+        <v>173</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>254</v>
       </c>
       <c r="C163" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D163" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E163">
-        <v>1026.0999999999999</v>
+        <v>15566.04</v>
       </c>
       <c r="F163" t="s">
-        <v>273</v>
+        <v>255</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A164">
-        <v>188</v>
-      </c>
-      <c r="B164" t="s">
-        <v>274</v>
+        <v>90</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>150</v>
       </c>
       <c r="C164" t="s">
         <v>29</v>
       </c>
       <c r="D164" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E164">
-        <v>19110.080000000002</v>
+        <v>17475.57</v>
       </c>
       <c r="F164" t="s">
-        <v>275</v>
+        <v>151</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A165">
-        <v>189</v>
-      </c>
-      <c r="B165" t="s">
-        <v>276</v>
+        <v>6</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="C165" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D165" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E165">
-        <v>11426.16</v>
+        <v>5786.35</v>
       </c>
       <c r="F165" t="s">
-        <v>277</v>
+        <v>25</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A166">
-        <v>190</v>
-      </c>
-      <c r="B166" t="s">
-        <v>132</v>
+        <v>59</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="C166" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="D166" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E166">
-        <v>13550.61</v>
+        <v>9420.8700000000008</v>
       </c>
       <c r="F166" t="s">
-        <v>278</v>
+        <v>110</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A167">
-        <v>191</v>
-      </c>
-      <c r="B167" t="s">
-        <v>279</v>
+        <v>99</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>162</v>
       </c>
       <c r="C167" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D167" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E167">
-        <v>4004.41</v>
+        <v>1478.93</v>
       </c>
       <c r="F167" t="s">
-        <v>55</v>
+        <v>163</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A168">
-        <v>193</v>
-      </c>
-      <c r="B168" t="s">
-        <v>280</v>
+        <v>5</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="C168" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D168" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E168">
-        <v>8588.7999999999993</v>
+        <v>7390.2</v>
       </c>
       <c r="F168" t="s">
-        <v>281</v>
+        <v>23</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A169">
-        <v>194</v>
-      </c>
-      <c r="B169" t="s">
-        <v>154</v>
+        <v>133</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>138</v>
       </c>
       <c r="C169" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D169" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E169">
-        <v>2275.15</v>
+        <v>5593.16</v>
       </c>
       <c r="F169" t="s">
-        <v>282</v>
+        <v>209</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A170">
-        <v>195</v>
-      </c>
-      <c r="B170" t="s">
-        <v>283</v>
+        <v>136</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="C170" t="s">
         <v>29</v>
@@ -4669,113 +4675,121 @@
         <v>22</v>
       </c>
       <c r="E170">
-        <v>18170.310000000001</v>
+        <v>8073.66</v>
       </c>
       <c r="F170" t="s">
-        <v>284</v>
+        <v>211</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A171">
-        <v>196</v>
-      </c>
-      <c r="B171" t="s">
-        <v>285</v>
+        <v>102</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>168</v>
       </c>
       <c r="C171" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="D171" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E171">
-        <v>15225.1</v>
+        <v>10186.549999999999</v>
       </c>
       <c r="F171" t="s">
-        <v>286</v>
+        <v>169</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A172">
-        <v>197</v>
-      </c>
-      <c r="B172" t="s">
-        <v>287</v>
+        <v>94</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>154</v>
       </c>
       <c r="C172" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="D172" t="s">
         <v>22</v>
       </c>
       <c r="E172">
-        <v>16460.68</v>
+        <v>6312.57</v>
       </c>
       <c r="F172" t="s">
-        <v>288</v>
+        <v>155</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A173">
-        <v>198</v>
-      </c>
-      <c r="B173" t="s">
-        <v>289</v>
+        <v>113</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>184</v>
       </c>
       <c r="C173" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D173" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E173">
-        <v>12795.28</v>
+        <v>1124.9100000000001</v>
       </c>
       <c r="F173" t="s">
-        <v>290</v>
+        <v>185</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A174">
-        <v>199</v>
-      </c>
-      <c r="B174" t="s">
-        <v>291</v>
+        <v>73</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="C174" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D174" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E174">
-        <v>9634.17</v>
+        <v>124.41</v>
       </c>
       <c r="F174" t="s">
-        <v>292</v>
+        <v>130</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A175">
-        <v>200</v>
-      </c>
-      <c r="B175" t="s">
-        <v>87</v>
+        <v>116</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>189</v>
       </c>
       <c r="C175" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D175" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E175">
-        <v>13022</v>
+        <v>17243.939999999999</v>
       </c>
       <c r="F175" t="s">
-        <v>293</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F175" xr:uid="{D2A49EED-A4B8-416A-B899-C02FD6CF124B}">
+    <sortState ref="A2:F175">
+      <sortCondition ref="D1:D175"/>
+    </sortState>
+  </autoFilter>
+  <sortState ref="A2:F175">
+    <sortCondition ref="B2:B175"/>
+  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>